--- a/बजेट माग estimate/thekka/ओखरबोट नेपालटोल लप्सिखोला सडक gravel/ओखरबोट नेपालटोल सडक  लप्सिखोला सडक gravel - sir.xlsx
+++ b/बजेट माग estimate/thekka/ओखरबोट नेपालटोल लप्सिखोला सडक gravel/ओखरबोट नेपालटोल सडक  लप्सिखोला सडक gravel - sir.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7CD690B-5EF3-4A04-80A1-77F11661A615}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0DB01B7-A765-470D-B881-0F93F7FF30AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
     <definedName name="description_781">#REF!</definedName>
     <definedName name="description_783">[1]Abstract!$B$301</definedName>
     <definedName name="description_784">[3]Abstract!$B$300</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">estimate!$A$1:$K$66</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">estimate!$A$1:$K$42</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">estimate!$1:$8</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="42">
   <si>
     <t>Government of Nepal</t>
   </si>
@@ -126,21 +126,6 @@
     <t>Total</t>
   </si>
   <si>
-    <t>-13% VAT for materials</t>
-  </si>
-  <si>
-    <t>Budget allocated</t>
-  </si>
-  <si>
-    <t>Municipal payment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contingencies </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maintanince </t>
-  </si>
-  <si>
     <t>F.Y.: 2082/2083</t>
   </si>
   <si>
@@ -150,24 +135,6 @@
     <t>Providing and laying of Plain/Reinforced Cement Concrete in Foundation complete as per Drawing and Technical Specifications, PCC Grade M 15</t>
   </si>
   <si>
-    <t>-13% VAT for cement</t>
-  </si>
-  <si>
-    <t>-13% VAT for sand</t>
-  </si>
-  <si>
-    <t>-13% VAT for aggregate</t>
-  </si>
-  <si>
-    <t>-13% VAT for formworks</t>
-  </si>
-  <si>
-    <t>-13% VAT for water</t>
-  </si>
-  <si>
-    <t>User contribution</t>
-  </si>
-  <si>
     <t>Date: 2082/09/06</t>
   </si>
   <si>
@@ -175,9 +142,6 @@
   </si>
   <si>
     <t>Earthwork Excavation in Cutting., Roadway Excavation in all types of Soil by Mechanical  Means ., Road way Excavation in  all types of soil as per Drawing and technical specifications  including  removal of stumps and other deleterious matter, all lifts and lead as per Drawing and instruction of the Engineer.</t>
-  </si>
-  <si>
-    <t>-13% VAT</t>
   </si>
   <si>
     <r>
@@ -208,18 +172,12 @@
     <t>Random Rubble Masonry, Providing and laying of Stone Masonry Work in Cement Mortar 1:6 in Foundation complete as per Drawing and Technical Specifications., Using Concrete Mixer</t>
   </si>
   <si>
-    <t>-13% VAT for stone</t>
-  </si>
-  <si>
     <t>Providing and Laying Reinforced cement concrete NP3 Flush jointed pipe for culverts including fixing with cement mortar 1:2 as per Drawing and Technical Specifications., 450 mm  internal dia.</t>
   </si>
   <si>
     <t>rm</t>
   </si>
   <si>
-    <t>-13% VAT for NP3 RCC pipe 450mm dia</t>
-  </si>
-  <si>
     <t>-450mm dia hume pipe</t>
   </si>
   <si>
@@ -227,18 +185,6 @@
   </si>
   <si>
     <t>cum</t>
-  </si>
-  <si>
-    <t>-13% VAT for sub-base material S1 type or S2 type</t>
-  </si>
-  <si>
-    <t>-13% VAT for mortar grader</t>
-  </si>
-  <si>
-    <t>-13% VAT for vibratory road roller</t>
-  </si>
-  <si>
-    <t>-13% VAT for tractor/loader</t>
   </si>
   <si>
     <t>Provisional sum for lab test</t>
@@ -423,7 +369,7 @@
     <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -514,8 +460,23 @@
     </xf>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -526,33 +487,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1080,7 +1014,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S66"/>
+  <dimension ref="A1:S42"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.7109375" style="19" customWidth="1"/>
@@ -1099,113 +1033,113 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="48"/>
-      <c r="H1" s="48"/>
-      <c r="I1" s="48"/>
-      <c r="J1" s="48"/>
-      <c r="K1" s="48"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
+      <c r="K1" s="40"/>
     </row>
     <row r="2" spans="1:16" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="49" t="s">
+      <c r="A2" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="49"/>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="49"/>
-      <c r="H2" s="49"/>
-      <c r="I2" s="49"/>
-      <c r="J2" s="49"/>
-      <c r="K2" s="49"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="41"/>
+      <c r="J2" s="41"/>
+      <c r="K2" s="41"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="50" t="s">
+      <c r="A3" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="50"/>
-      <c r="C3" s="50"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="50"/>
-      <c r="F3" s="50"/>
-      <c r="G3" s="50"/>
-      <c r="H3" s="50"/>
-      <c r="I3" s="50"/>
-      <c r="J3" s="50"/>
-      <c r="K3" s="50"/>
+      <c r="B3" s="42"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="42"/>
+      <c r="H3" s="42"/>
+      <c r="I3" s="42"/>
+      <c r="J3" s="42"/>
+      <c r="K3" s="42"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" s="50" t="s">
+      <c r="A4" s="42" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="50"/>
-      <c r="C4" s="50"/>
-      <c r="D4" s="50"/>
-      <c r="E4" s="50"/>
-      <c r="F4" s="50"/>
-      <c r="G4" s="50"/>
-      <c r="H4" s="50"/>
-      <c r="I4" s="50"/>
-      <c r="J4" s="50"/>
-      <c r="K4" s="50"/>
+      <c r="B4" s="42"/>
+      <c r="C4" s="42"/>
+      <c r="D4" s="42"/>
+      <c r="E4" s="42"/>
+      <c r="F4" s="42"/>
+      <c r="G4" s="42"/>
+      <c r="H4" s="42"/>
+      <c r="I4" s="42"/>
+      <c r="J4" s="42"/>
+      <c r="K4" s="42"/>
     </row>
     <row r="5" spans="1:16" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="51" t="s">
+      <c r="A5" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="51"/>
-      <c r="C5" s="51"/>
-      <c r="D5" s="51"/>
-      <c r="E5" s="51"/>
-      <c r="F5" s="51"/>
-      <c r="G5" s="51"/>
-      <c r="H5" s="51"/>
-      <c r="I5" s="51"/>
-      <c r="J5" s="51"/>
-      <c r="K5" s="51"/>
+      <c r="B5" s="43"/>
+      <c r="C5" s="43"/>
+      <c r="D5" s="43"/>
+      <c r="E5" s="43"/>
+      <c r="F5" s="43"/>
+      <c r="G5" s="43"/>
+      <c r="H5" s="43"/>
+      <c r="I5" s="43"/>
+      <c r="J5" s="43"/>
+      <c r="K5" s="43"/>
     </row>
     <row r="6" spans="1:16" ht="18" x14ac:dyDescent="0.25">
-      <c r="A6" s="46" t="s">
-        <v>40</v>
-      </c>
-      <c r="B6" s="46"/>
-      <c r="C6" s="46"/>
-      <c r="D6" s="46"/>
-      <c r="E6" s="46"/>
-      <c r="F6" s="46"/>
+      <c r="A6" s="38" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="38"/>
+      <c r="C6" s="38"/>
+      <c r="D6" s="38"/>
+      <c r="E6" s="38"/>
+      <c r="F6" s="38"/>
       <c r="G6" s="10"/>
-      <c r="H6" s="47" t="s">
-        <v>27</v>
-      </c>
-      <c r="I6" s="47"/>
-      <c r="J6" s="47"/>
-      <c r="K6" s="47"/>
+      <c r="H6" s="39" t="s">
+        <v>22</v>
+      </c>
+      <c r="I6" s="39"/>
+      <c r="J6" s="39"/>
+      <c r="K6" s="39"/>
     </row>
     <row r="7" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="41" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="41"/>
-      <c r="C7" s="41"/>
-      <c r="D7" s="41"/>
-      <c r="E7" s="41"/>
-      <c r="F7" s="41"/>
+      <c r="A7" s="46" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="46"/>
+      <c r="C7" s="46"/>
+      <c r="D7" s="46"/>
+      <c r="E7" s="46"/>
+      <c r="F7" s="46"/>
       <c r="G7" s="11"/>
-      <c r="H7" s="42" t="s">
-        <v>36</v>
-      </c>
-      <c r="I7" s="42"/>
-      <c r="J7" s="42"/>
-      <c r="K7" s="42"/>
+      <c r="H7" s="47" t="s">
+        <v>25</v>
+      </c>
+      <c r="I7" s="47"/>
+      <c r="J7" s="47"/>
+      <c r="K7" s="47"/>
     </row>
     <row r="8" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
@@ -1247,7 +1181,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="35" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="C9" s="17"/>
       <c r="D9" s="17"/>
@@ -1262,7 +1196,7 @@
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="16"/>
       <c r="B10" s="32" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="C10" s="37">
         <v>0.5</v>
@@ -1301,7 +1235,7 @@
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="16"/>
       <c r="B11" s="32" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="C11" s="17">
         <v>1</v>
@@ -1333,7 +1267,7 @@
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="16"/>
       <c r="B12" s="32" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="C12" s="17">
         <v>2</v>
@@ -1377,19 +1311,18 @@
         <v>17</v>
       </c>
       <c r="I13" s="6">
-        <v>62.95</v>
+        <f>1.15*62.95</f>
+        <v>72.392499999999998</v>
       </c>
       <c r="J13" s="18">
         <f>G13*I13</f>
-        <v>6880.7497500000009</v>
+        <v>7912.8622125000002</v>
       </c>
       <c r="K13" s="5"/>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="16"/>
-      <c r="B14" s="32" t="s">
-        <v>39</v>
-      </c>
+      <c r="B14" s="17"/>
       <c r="C14" s="17"/>
       <c r="D14" s="17"/>
       <c r="E14" s="17"/>
@@ -1397,15 +1330,16 @@
       <c r="G14" s="17"/>
       <c r="H14" s="17"/>
       <c r="I14" s="17"/>
-      <c r="J14" s="18">
-        <f>0.13*G13*18612/360</f>
-        <v>734.63890500000014</v>
-      </c>
+      <c r="J14" s="17"/>
       <c r="K14" s="17"/>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A15" s="16"/>
-      <c r="B15" s="17"/>
+    <row r="15" spans="1:16" ht="110.25" x14ac:dyDescent="0.25">
+      <c r="A15" s="16">
+        <v>2</v>
+      </c>
+      <c r="B15" s="35" t="s">
+        <v>23</v>
+      </c>
       <c r="C15" s="17"/>
       <c r="D15" s="17"/>
       <c r="E15" s="17"/>
@@ -1416,86 +1350,85 @@
       <c r="J15" s="17"/>
       <c r="K15" s="17"/>
     </row>
-    <row r="16" spans="1:16" ht="110.25" x14ac:dyDescent="0.25">
-      <c r="A16" s="16">
-        <v>2</v>
-      </c>
-      <c r="B16" s="35" t="s">
-        <v>28</v>
-      </c>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="17"/>
-      <c r="G16" s="17"/>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A16" s="16"/>
+      <c r="B16" s="32" t="str">
+        <f>B11</f>
+        <v>-for mangaal</v>
+      </c>
+      <c r="C16" s="17">
+        <f>C11</f>
+        <v>1</v>
+      </c>
+      <c r="D16" s="33">
+        <f>D11</f>
+        <v>1.8</v>
+      </c>
+      <c r="E16" s="33">
+        <f>E11</f>
+        <v>1.8</v>
+      </c>
+      <c r="F16" s="33">
+        <v>0.15</v>
+      </c>
+      <c r="G16" s="33">
+        <f>PRODUCT(C16:F16)</f>
+        <v>0.48599999999999999</v>
+      </c>
       <c r="H16" s="17"/>
       <c r="I16" s="17"/>
       <c r="J16" s="17"/>
       <c r="K16" s="17"/>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A17" s="16"/>
-      <c r="B17" s="32" t="str">
-        <f>B11</f>
-        <v>-for mangaal</v>
-      </c>
-      <c r="C17" s="17">
-        <f>C11</f>
-        <v>1</v>
-      </c>
-      <c r="D17" s="33">
-        <f>D11</f>
-        <v>1.8</v>
-      </c>
-      <c r="E17" s="33">
-        <f>E11</f>
-        <v>1.8</v>
-      </c>
-      <c r="F17" s="33">
-        <v>0.15</v>
-      </c>
-      <c r="G17" s="33">
-        <f>PRODUCT(C17:F17)</f>
+      <c r="M16" s="36"/>
+      <c r="N16" s="36"/>
+      <c r="O16" s="36"/>
+      <c r="P16" s="36"/>
+    </row>
+    <row r="17" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2"/>
+      <c r="B17" s="34" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" s="3"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="6">
+        <f>SUM(G16:G16)</f>
         <v>0.48599999999999999</v>
       </c>
-      <c r="H17" s="17"/>
-      <c r="I17" s="17"/>
-      <c r="J17" s="17"/>
-      <c r="K17" s="17"/>
-      <c r="M17" s="36"/>
-      <c r="N17" s="36"/>
-      <c r="O17" s="36"/>
-      <c r="P17" s="36"/>
-    </row>
-    <row r="18" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="2"/>
-      <c r="B18" s="34" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" s="3"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="6">
-        <f>SUM(G17:G17)</f>
-        <v>0.48599999999999999</v>
-      </c>
-      <c r="H18" s="7" t="s">
+      <c r="H17" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I18" s="6">
-        <v>4458.5200000000004</v>
-      </c>
-      <c r="J18" s="18">
-        <f>G18*I18</f>
-        <v>2166.8407200000001</v>
-      </c>
-      <c r="K18" s="5"/>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A19" s="16"/>
-      <c r="B19" s="32" t="s">
-        <v>22</v>
+      <c r="I17" s="6">
+        <f>1.15*4458.52</f>
+        <v>5127.2979999999998</v>
+      </c>
+      <c r="J17" s="18">
+        <f>G17*I17</f>
+        <v>2491.8668279999997</v>
+      </c>
+      <c r="K17" s="5"/>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A18" s="16"/>
+      <c r="B18" s="17"/>
+      <c r="C18" s="17"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="17"/>
+      <c r="F18" s="17"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="17"/>
+      <c r="I18" s="17"/>
+      <c r="J18" s="17"/>
+      <c r="K18" s="17"/>
+    </row>
+    <row r="19" spans="1:16" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A19" s="16">
+        <v>3</v>
+      </c>
+      <c r="B19" s="35" t="s">
+        <v>24</v>
       </c>
       <c r="C19" s="17"/>
       <c r="D19" s="17"/>
@@ -1504,173 +1437,191 @@
       <c r="G19" s="17"/>
       <c r="H19" s="17"/>
       <c r="I19" s="17"/>
-      <c r="J19" s="18">
-        <f>0.13*G18*(14817.6)/5</f>
-        <v>187.2351936</v>
-      </c>
+      <c r="J19" s="17"/>
       <c r="K19" s="17"/>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="16"/>
-      <c r="B20" s="17"/>
-      <c r="C20" s="17"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="17"/>
+      <c r="B20" s="32" t="str">
+        <f>B16</f>
+        <v>-for mangaal</v>
+      </c>
+      <c r="C20" s="17">
+        <f>C16</f>
+        <v>1</v>
+      </c>
+      <c r="D20" s="33">
+        <f>D16</f>
+        <v>1.8</v>
+      </c>
+      <c r="E20" s="33">
+        <f>E16</f>
+        <v>1.8</v>
+      </c>
+      <c r="F20" s="33">
+        <v>0.1</v>
+      </c>
+      <c r="G20" s="33">
+        <f>PRODUCT(C20:F20)</f>
+        <v>0.32400000000000007</v>
+      </c>
       <c r="H20" s="17"/>
       <c r="I20" s="17"/>
       <c r="J20" s="17"/>
       <c r="K20" s="17"/>
-    </row>
-    <row r="21" spans="1:16" ht="94.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="16">
-        <v>3</v>
-      </c>
-      <c r="B21" s="35" t="s">
-        <v>29</v>
-      </c>
-      <c r="C21" s="17"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="17"/>
-      <c r="G21" s="17"/>
+      <c r="M20" s="36"/>
+      <c r="N20" s="36"/>
+      <c r="O20" s="36"/>
+      <c r="P20" s="36"/>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A21" s="16"/>
+      <c r="B21" s="32" t="s">
+        <v>41</v>
+      </c>
+      <c r="C21" s="17">
+        <v>1</v>
+      </c>
+      <c r="D21" s="33">
+        <f>1.8+1.8+0.9+0.9</f>
+        <v>5.4</v>
+      </c>
+      <c r="E21" s="33">
+        <v>0.45</v>
+      </c>
+      <c r="F21" s="33">
+        <v>0.05</v>
+      </c>
+      <c r="G21" s="33">
+        <f>PRODUCT(C21:F21)</f>
+        <v>0.12150000000000001</v>
+      </c>
       <c r="H21" s="17"/>
       <c r="I21" s="17"/>
       <c r="J21" s="17"/>
       <c r="K21" s="17"/>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A22" s="16"/>
-      <c r="B22" s="32" t="str">
-        <f>B17</f>
-        <v>-for mangaal</v>
-      </c>
-      <c r="C22" s="17">
-        <f>C17</f>
-        <v>1</v>
-      </c>
-      <c r="D22" s="33">
-        <f>D17</f>
-        <v>1.8</v>
-      </c>
-      <c r="E22" s="33">
-        <f>E17</f>
-        <v>1.8</v>
-      </c>
-      <c r="F22" s="33">
-        <v>0.1</v>
-      </c>
-      <c r="G22" s="33">
-        <f>PRODUCT(C22:F22)</f>
-        <v>0.32400000000000007</v>
-      </c>
-      <c r="H22" s="17"/>
-      <c r="I22" s="17"/>
-      <c r="J22" s="17"/>
-      <c r="K22" s="17"/>
-      <c r="M22" s="36"/>
-      <c r="N22" s="36"/>
-      <c r="O22" s="36"/>
-      <c r="P22" s="36"/>
+      <c r="M21" s="36"/>
+      <c r="N21" s="36"/>
+      <c r="O21" s="36"/>
+      <c r="P21" s="36"/>
+    </row>
+    <row r="22" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2"/>
+      <c r="B22" s="34" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" s="3"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="6">
+        <f>SUM(G20:G21)</f>
+        <v>0.44550000000000006</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I22" s="6">
+        <f>1.15*10964.46</f>
+        <v>12609.128999999997</v>
+      </c>
+      <c r="J22" s="18">
+        <f>G22*I22</f>
+        <v>5617.3669694999999</v>
+      </c>
+      <c r="K22" s="5"/>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="16"/>
-      <c r="B23" s="32" t="s">
-        <v>59</v>
-      </c>
-      <c r="C23" s="17">
-        <v>1</v>
-      </c>
-      <c r="D23" s="33">
-        <f>1.8+1.8+0.9+0.9</f>
-        <v>5.4</v>
-      </c>
-      <c r="E23" s="33">
-        <v>0.45</v>
-      </c>
-      <c r="F23" s="33">
-        <v>0.05</v>
-      </c>
-      <c r="G23" s="33">
-        <f>PRODUCT(C23:F23)</f>
-        <v>0.12150000000000001</v>
-      </c>
+      <c r="B23" s="17"/>
+      <c r="C23" s="17"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="17"/>
+      <c r="G23" s="17"/>
       <c r="H23" s="17"/>
       <c r="I23" s="17"/>
       <c r="J23" s="17"/>
       <c r="K23" s="17"/>
-      <c r="M23" s="36"/>
-      <c r="N23" s="36"/>
-      <c r="O23" s="36"/>
-      <c r="P23" s="36"/>
-    </row>
-    <row r="24" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="2"/>
-      <c r="B24" s="34" t="s">
-        <v>16</v>
-      </c>
-      <c r="C24" s="3"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="6">
-        <f>SUM(G22:G23)</f>
-        <v>0.44550000000000006</v>
-      </c>
-      <c r="H24" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="I24" s="6">
-        <v>10964.46</v>
-      </c>
-      <c r="J24" s="18">
-        <f>G24*I24</f>
-        <v>4884.6669300000003</v>
-      </c>
-      <c r="K24" s="5"/>
+    </row>
+    <row r="24" spans="1:16" ht="110.25" x14ac:dyDescent="0.25">
+      <c r="A24" s="16">
+        <v>4</v>
+      </c>
+      <c r="B24" s="35" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24" s="17"/>
+      <c r="D24" s="17"/>
+      <c r="E24" s="17"/>
+      <c r="F24" s="17"/>
+      <c r="G24" s="17"/>
+      <c r="H24" s="17"/>
+      <c r="I24" s="17"/>
+      <c r="J24" s="17"/>
+      <c r="K24" s="17"/>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="16"/>
-      <c r="B25" s="32" t="s">
-        <v>30</v>
-      </c>
-      <c r="C25" s="17"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="17"/>
-      <c r="G25" s="17"/>
+      <c r="B25" s="32" t="str">
+        <f>B20</f>
+        <v>-for mangaal</v>
+      </c>
+      <c r="C25" s="17">
+        <v>1</v>
+      </c>
+      <c r="D25" s="33">
+        <f>0.9+0.9+1.8+1.8</f>
+        <v>5.4</v>
+      </c>
+      <c r="E25" s="33">
+        <v>0.45</v>
+      </c>
+      <c r="F25" s="33">
+        <v>0.75</v>
+      </c>
+      <c r="G25" s="33">
+        <f>PRODUCT(C25:F25)</f>
+        <v>1.8225000000000002</v>
+      </c>
       <c r="H25" s="17"/>
       <c r="I25" s="17"/>
-      <c r="J25" s="18">
-        <f>0.13*G24*(53818.03)/15</f>
-        <v>207.79141383000004</v>
-      </c>
+      <c r="J25" s="17"/>
       <c r="K25" s="17"/>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A26" s="16"/>
-      <c r="B26" s="32" t="s">
-        <v>31</v>
-      </c>
-      <c r="C26" s="17"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="17"/>
-      <c r="G26" s="17"/>
-      <c r="H26" s="17"/>
-      <c r="I26" s="17"/>
+      <c r="M25" s="36"/>
+      <c r="N25" s="36"/>
+      <c r="O25" s="36"/>
+      <c r="P25" s="36"/>
+    </row>
+    <row r="26" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2"/>
+      <c r="B26" s="34" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" s="3"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="6">
+        <f>SUM(G25:G25)</f>
+        <v>1.8225000000000002</v>
+      </c>
+      <c r="H26" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I26" s="6">
+        <f>1.15*8987.83</f>
+        <v>10336.004499999999</v>
+      </c>
       <c r="J26" s="18">
-        <f>0.13*G24*(21432.6)/15</f>
-        <v>82.751268600000003</v>
-      </c>
-      <c r="K26" s="17"/>
+        <f>G26*I26</f>
+        <v>18837.368201249999</v>
+      </c>
+      <c r="K26" s="5"/>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" s="16"/>
-      <c r="B27" s="32" t="s">
-        <v>32</v>
-      </c>
+      <c r="B27" s="17"/>
       <c r="C27" s="17"/>
       <c r="D27" s="17"/>
       <c r="E27" s="17"/>
@@ -1678,16 +1629,15 @@
       <c r="G27" s="17"/>
       <c r="H27" s="17"/>
       <c r="I27" s="17"/>
-      <c r="J27" s="18">
-        <f>0.13*G24*(25719.12+13573.98+4286.52)/15</f>
-        <v>168.26091282000002</v>
-      </c>
+      <c r="J27" s="17"/>
       <c r="K27" s="17"/>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A28" s="16"/>
-      <c r="B28" s="32" t="s">
-        <v>33</v>
+    <row r="28" spans="1:16" ht="110.25" x14ac:dyDescent="0.25">
+      <c r="A28" s="16">
+        <v>5</v>
+      </c>
+      <c r="B28" s="35" t="s">
+        <v>34</v>
       </c>
       <c r="C28" s="17"/>
       <c r="D28" s="17"/>
@@ -1696,50 +1646,64 @@
       <c r="G28" s="17"/>
       <c r="H28" s="17"/>
       <c r="I28" s="17"/>
-      <c r="J28" s="18">
-        <f>0.13*G24*(6325.7)/15</f>
-        <v>24.423527700000005</v>
-      </c>
+      <c r="J28" s="17"/>
       <c r="K28" s="17"/>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="16"/>
       <c r="B29" s="32" t="s">
-        <v>34</v>
-      </c>
-      <c r="C29" s="17"/>
-      <c r="D29" s="17"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="17"/>
-      <c r="G29" s="17"/>
+        <v>36</v>
+      </c>
+      <c r="C29" s="17">
+        <v>2</v>
+      </c>
+      <c r="D29" s="33">
+        <v>2.5</v>
+      </c>
+      <c r="E29" s="33"/>
+      <c r="F29" s="33"/>
+      <c r="G29" s="33">
+        <f>PRODUCT(C29:F29)</f>
+        <v>5</v>
+      </c>
       <c r="H29" s="17"/>
       <c r="I29" s="17"/>
-      <c r="J29" s="18">
-        <f>0.13*G24*(310)/5</f>
-        <v>3.5907300000000006</v>
-      </c>
+      <c r="J29" s="17"/>
       <c r="K29" s="17"/>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A30" s="16"/>
-      <c r="B30" s="17"/>
-      <c r="C30" s="17"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="17"/>
-      <c r="G30" s="17"/>
-      <c r="H30" s="17"/>
-      <c r="I30" s="17"/>
-      <c r="J30" s="17"/>
-      <c r="K30" s="17"/>
-    </row>
-    <row r="31" spans="1:16" ht="110.25" x14ac:dyDescent="0.25">
-      <c r="A31" s="16">
-        <v>4</v>
-      </c>
-      <c r="B31" s="35" t="s">
-        <v>45</v>
-      </c>
+      <c r="M29" s="36"/>
+      <c r="N29" s="36"/>
+      <c r="O29" s="36"/>
+      <c r="P29" s="36"/>
+    </row>
+    <row r="30" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="2"/>
+      <c r="B30" s="34" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30" s="3"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="5"/>
+      <c r="F30" s="5"/>
+      <c r="G30" s="6">
+        <f>SUM(G29:G29)</f>
+        <v>5</v>
+      </c>
+      <c r="H30" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="I30" s="6">
+        <f>1.15*5160.18</f>
+        <v>5934.2069999999994</v>
+      </c>
+      <c r="J30" s="18">
+        <f>G30*I30</f>
+        <v>29671.034999999996</v>
+      </c>
+      <c r="K30" s="5"/>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A31" s="16"/>
+      <c r="B31" s="17"/>
       <c r="C31" s="17"/>
       <c r="D31" s="17"/>
       <c r="E31" s="17"/>
@@ -1750,86 +1714,85 @@
       <c r="J31" s="17"/>
       <c r="K31" s="17"/>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A32" s="16"/>
-      <c r="B32" s="32" t="str">
-        <f>B22</f>
-        <v>-for mangaal</v>
-      </c>
-      <c r="C32" s="17">
-        <v>1</v>
-      </c>
-      <c r="D32" s="33">
-        <f>0.9+0.9+1.8+1.8</f>
-        <v>5.4</v>
-      </c>
-      <c r="E32" s="33">
-        <v>0.45</v>
-      </c>
-      <c r="F32" s="33">
-        <v>0.75</v>
-      </c>
-      <c r="G32" s="33">
-        <f>PRODUCT(C32:F32)</f>
-        <v>1.8225000000000002</v>
-      </c>
+    <row r="32" spans="1:16" ht="121.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="16">
+        <v>6</v>
+      </c>
+      <c r="B32" s="35" t="s">
+        <v>37</v>
+      </c>
+      <c r="C32" s="17"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="17"/>
+      <c r="F32" s="17"/>
+      <c r="G32" s="17"/>
       <c r="H32" s="17"/>
       <c r="I32" s="17"/>
       <c r="J32" s="17"/>
       <c r="K32" s="17"/>
-      <c r="M32" s="36"/>
-      <c r="N32" s="36"/>
-      <c r="O32" s="36"/>
-      <c r="P32" s="36"/>
-    </row>
-    <row r="33" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="2"/>
-      <c r="B33" s="34" t="s">
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A33" s="16"/>
+      <c r="B33" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="C33" s="37">
+        <f>C10</f>
+        <v>0.5</v>
+      </c>
+      <c r="D33" s="33">
+        <f>D10</f>
+        <v>400</v>
+      </c>
+      <c r="E33" s="33">
+        <f>E10</f>
+        <v>3.5</v>
+      </c>
+      <c r="F33" s="33">
+        <v>0.15</v>
+      </c>
+      <c r="G33" s="33">
+        <f>PRODUCT(C33:F33)</f>
+        <v>105</v>
+      </c>
+      <c r="H33" s="17"/>
+      <c r="I33" s="17"/>
+      <c r="J33" s="17"/>
+      <c r="K33" s="17"/>
+      <c r="M33" s="36"/>
+      <c r="N33" s="36"/>
+      <c r="O33" s="36"/>
+      <c r="P33" s="36"/>
+    </row>
+    <row r="34" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="2"/>
+      <c r="B34" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="C33" s="3"/>
-      <c r="D33" s="4"/>
-      <c r="E33" s="5"/>
-      <c r="F33" s="5"/>
-      <c r="G33" s="6">
-        <f>SUM(G32:G32)</f>
-        <v>1.8225000000000002</v>
-      </c>
-      <c r="H33" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="I33" s="6">
-        <v>8987.83</v>
-      </c>
-      <c r="J33" s="18">
-        <f>G33*I33</f>
-        <v>16380.320175000003</v>
-      </c>
-      <c r="K33" s="5"/>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A34" s="16"/>
-      <c r="B34" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="C34" s="17"/>
-      <c r="D34" s="17"/>
-      <c r="E34" s="17"/>
-      <c r="F34" s="17"/>
-      <c r="G34" s="17"/>
-      <c r="H34" s="17"/>
-      <c r="I34" s="17"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="5"/>
+      <c r="F34" s="5"/>
+      <c r="G34" s="6">
+        <f>SUM(G33:G33)</f>
+        <v>105</v>
+      </c>
+      <c r="H34" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="I34" s="6">
+        <f>1.15*2976.7</f>
+        <v>3423.2049999999995</v>
+      </c>
       <c r="J34" s="18">
-        <f>0.13*G33*(14808.78)/5</f>
-        <v>701.71404030000008</v>
-      </c>
-      <c r="K34" s="17"/>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+        <f>G34*I34</f>
+        <v>359436.52499999997</v>
+      </c>
+      <c r="K34" s="5"/>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A35" s="16"/>
-      <c r="B35" s="32" t="s">
-        <v>30</v>
-      </c>
+      <c r="B35" s="17"/>
       <c r="C35" s="17"/>
       <c r="D35" s="17"/>
       <c r="E35" s="17"/>
@@ -1837,578 +1800,150 @@
       <c r="G35" s="17"/>
       <c r="H35" s="17"/>
       <c r="I35" s="17"/>
-      <c r="J35" s="18">
-        <f>0.13*G33*5863.95/5</f>
-        <v>277.86327075000003</v>
-      </c>
+      <c r="J35" s="17"/>
       <c r="K35" s="17"/>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A36" s="16"/>
-      <c r="B36" s="32" t="s">
-        <v>31</v>
-      </c>
-      <c r="C36" s="17"/>
-      <c r="D36" s="17"/>
-      <c r="E36" s="17"/>
-      <c r="F36" s="17"/>
-      <c r="G36" s="17"/>
-      <c r="H36" s="17"/>
-      <c r="I36" s="17"/>
-      <c r="J36" s="18">
-        <f>0.13*G33*6604.416/5</f>
-        <v>312.95025216000005</v>
-      </c>
-      <c r="K36" s="17"/>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A37" s="16"/>
-      <c r="B37" s="32" t="s">
-        <v>34</v>
-      </c>
-      <c r="C37" s="17"/>
-      <c r="D37" s="17"/>
-      <c r="E37" s="17"/>
-      <c r="F37" s="17"/>
-      <c r="G37" s="17"/>
-      <c r="H37" s="17"/>
-      <c r="I37" s="17"/>
-      <c r="J37" s="18">
-        <f>0.13*G33*310/5</f>
-        <v>14.689350000000001</v>
-      </c>
-      <c r="K37" s="17"/>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A38" s="16"/>
-      <c r="B38" s="17"/>
-      <c r="C38" s="17"/>
-      <c r="D38" s="17"/>
-      <c r="E38" s="17"/>
-      <c r="F38" s="17"/>
-      <c r="G38" s="17"/>
-      <c r="H38" s="17"/>
-      <c r="I38" s="17"/>
-      <c r="J38" s="17"/>
-      <c r="K38" s="17"/>
-    </row>
-    <row r="39" spans="1:16" ht="110.25" x14ac:dyDescent="0.25">
-      <c r="A39" s="16">
-        <v>5</v>
-      </c>
-      <c r="B39" s="35" t="s">
-        <v>47</v>
-      </c>
-      <c r="C39" s="17"/>
-      <c r="D39" s="17"/>
-      <c r="E39" s="17"/>
-      <c r="F39" s="17"/>
-      <c r="G39" s="17"/>
-      <c r="H39" s="17"/>
-      <c r="I39" s="17"/>
-      <c r="J39" s="17"/>
-      <c r="K39" s="17"/>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A40" s="16"/>
-      <c r="B40" s="32" t="s">
-        <v>50</v>
-      </c>
-      <c r="C40" s="17">
-        <v>2</v>
-      </c>
-      <c r="D40" s="33">
-        <v>2.5</v>
-      </c>
-      <c r="E40" s="33"/>
-      <c r="F40" s="33"/>
-      <c r="G40" s="33">
-        <f>PRODUCT(C40:F40)</f>
-        <v>5</v>
-      </c>
-      <c r="H40" s="17"/>
-      <c r="I40" s="17"/>
-      <c r="J40" s="17"/>
-      <c r="K40" s="17"/>
-      <c r="M40" s="36"/>
-      <c r="N40" s="36"/>
-      <c r="O40" s="36"/>
-      <c r="P40" s="36"/>
-    </row>
-    <row r="41" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="2"/>
-      <c r="B41" s="34" t="s">
-        <v>16</v>
-      </c>
-      <c r="C41" s="3"/>
-      <c r="D41" s="4"/>
-      <c r="E41" s="5"/>
-      <c r="F41" s="5"/>
-      <c r="G41" s="6">
-        <f>SUM(G40:G40)</f>
-        <v>5</v>
-      </c>
-      <c r="H41" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="I41" s="6">
-        <v>5160.18</v>
-      </c>
-      <c r="J41" s="18">
-        <f>G41*I41</f>
-        <v>25800.9</v>
-      </c>
-      <c r="K41" s="5"/>
-    </row>
-    <row r="42" spans="1:16" ht="30" x14ac:dyDescent="0.25">
-      <c r="A42" s="16"/>
-      <c r="B42" s="38" t="s">
-        <v>49</v>
-      </c>
-      <c r="C42" s="17"/>
-      <c r="D42" s="17"/>
-      <c r="E42" s="17"/>
-      <c r="F42" s="17"/>
-      <c r="G42" s="17"/>
-      <c r="H42" s="17"/>
-      <c r="I42" s="17"/>
-      <c r="J42" s="18">
-        <f>0.13*G41*(56250)/12.5</f>
-        <v>2925</v>
-      </c>
-      <c r="K42" s="17"/>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A43" s="16"/>
-      <c r="B43" s="32" t="s">
-        <v>30</v>
-      </c>
-      <c r="C43" s="17"/>
-      <c r="D43" s="17"/>
-      <c r="E43" s="17"/>
-      <c r="F43" s="17"/>
-      <c r="G43" s="17"/>
-      <c r="H43" s="17"/>
-      <c r="I43" s="17"/>
-      <c r="J43" s="18">
-        <f>0.13*G41*912.17/12.5</f>
-        <v>47.432839999999999</v>
-      </c>
-      <c r="K43" s="17"/>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A44" s="16"/>
-      <c r="B44" s="32" t="s">
-        <v>31</v>
-      </c>
-      <c r="C44" s="17"/>
-      <c r="D44" s="17"/>
-      <c r="E44" s="17"/>
-      <c r="F44" s="17"/>
-      <c r="G44" s="17"/>
-      <c r="H44" s="17"/>
-      <c r="I44" s="17"/>
-      <c r="J44" s="18">
-        <f>0.13*G41*279.4176/12.5</f>
-        <v>14.5297152</v>
-      </c>
-      <c r="K44" s="17"/>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A45" s="16"/>
-      <c r="B45" s="17"/>
-      <c r="C45" s="17"/>
-      <c r="D45" s="17"/>
-      <c r="E45" s="17"/>
-      <c r="F45" s="17"/>
-      <c r="G45" s="17"/>
-      <c r="H45" s="17"/>
-      <c r="I45" s="17"/>
-      <c r="J45" s="17"/>
-      <c r="K45" s="17"/>
-    </row>
-    <row r="46" spans="1:16" ht="121.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="16">
-        <v>6</v>
-      </c>
-      <c r="B46" s="35" t="s">
-        <v>51</v>
-      </c>
-      <c r="C46" s="17"/>
-      <c r="D46" s="17"/>
-      <c r="E46" s="17"/>
-      <c r="F46" s="17"/>
-      <c r="G46" s="17"/>
-      <c r="H46" s="17"/>
-      <c r="I46" s="17"/>
-      <c r="J46" s="17"/>
-      <c r="K46" s="17"/>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A47" s="16"/>
-      <c r="B47" s="32" t="s">
-        <v>42</v>
-      </c>
-      <c r="C47" s="37">
-        <f>C10</f>
-        <v>0.5</v>
-      </c>
-      <c r="D47" s="33">
-        <f>D10</f>
-        <v>400</v>
-      </c>
-      <c r="E47" s="33">
-        <f>E10</f>
-        <v>3.5</v>
-      </c>
-      <c r="F47" s="33">
-        <v>0.15</v>
-      </c>
-      <c r="G47" s="33">
-        <f>PRODUCT(C47:F47)</f>
-        <v>105</v>
-      </c>
-      <c r="H47" s="17"/>
-      <c r="I47" s="17"/>
-      <c r="J47" s="17"/>
-      <c r="K47" s="17"/>
-      <c r="M47" s="36"/>
-      <c r="N47" s="36"/>
-      <c r="O47" s="36"/>
-      <c r="P47" s="36"/>
-    </row>
-    <row r="48" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="2"/>
-      <c r="B48" s="34" t="s">
-        <v>16</v>
-      </c>
-      <c r="C48" s="3"/>
-      <c r="D48" s="4"/>
-      <c r="E48" s="5"/>
-      <c r="F48" s="5"/>
-      <c r="G48" s="6">
-        <f>SUM(G47:G47)</f>
-        <v>105</v>
-      </c>
-      <c r="H48" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="I48" s="6">
-        <v>2976.7</v>
-      </c>
-      <c r="J48" s="18">
-        <f>G48*I48</f>
-        <v>312553.5</v>
-      </c>
-      <c r="K48" s="5"/>
-    </row>
-    <row r="49" spans="1:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="A49" s="16"/>
-      <c r="B49" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="C49" s="17"/>
-      <c r="D49" s="17"/>
-      <c r="E49" s="17"/>
-      <c r="F49" s="17"/>
-      <c r="G49" s="17"/>
-      <c r="H49" s="17"/>
-      <c r="I49" s="17"/>
-      <c r="J49" s="18">
-        <f>0.13*G48*826398.72/300</f>
-        <v>37601.141759999999</v>
-      </c>
-      <c r="K49" s="17"/>
-    </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A50" s="16"/>
-      <c r="B50" s="32" t="s">
-        <v>34</v>
-      </c>
-      <c r="C50" s="17"/>
-      <c r="D50" s="17"/>
-      <c r="E50" s="17"/>
-      <c r="F50" s="17"/>
-      <c r="G50" s="17"/>
-      <c r="H50" s="17"/>
-      <c r="I50" s="17"/>
-      <c r="J50" s="18">
-        <f>0.13*G48*5580/300</f>
-        <v>253.89</v>
-      </c>
-      <c r="K50" s="17"/>
-    </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A51" s="16"/>
-      <c r="B51" s="32" t="s">
-        <v>54</v>
-      </c>
-      <c r="C51" s="17"/>
-      <c r="D51" s="17"/>
-      <c r="E51" s="17"/>
-      <c r="F51" s="17"/>
-      <c r="G51" s="17"/>
-      <c r="H51" s="17"/>
-      <c r="I51" s="17"/>
-      <c r="J51" s="18">
-        <f>0.13*G48*17490/300</f>
-        <v>795.79499999999996</v>
-      </c>
-      <c r="K51" s="17"/>
-    </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A52" s="16"/>
-      <c r="B52" s="32" t="s">
-        <v>55</v>
-      </c>
-      <c r="C52" s="17"/>
-      <c r="D52" s="17"/>
-      <c r="E52" s="17"/>
-      <c r="F52" s="17"/>
-      <c r="G52" s="17"/>
-      <c r="H52" s="17"/>
-      <c r="I52" s="17"/>
-      <c r="J52" s="18">
-        <f>0.13*G48*19416/300</f>
-        <v>883.42800000000011</v>
-      </c>
-      <c r="K52" s="17"/>
-    </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A53" s="16"/>
-      <c r="B53" s="32" t="s">
-        <v>56</v>
-      </c>
-      <c r="C53" s="17"/>
-      <c r="D53" s="17"/>
-      <c r="E53" s="17"/>
-      <c r="F53" s="17"/>
-      <c r="G53" s="17"/>
-      <c r="H53" s="17"/>
-      <c r="I53" s="17"/>
-      <c r="J53" s="18">
-        <f>0.13*G48*10416/300</f>
-        <v>473.928</v>
-      </c>
-      <c r="K53" s="17"/>
-    </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A54" s="16"/>
-      <c r="B54" s="17"/>
-      <c r="C54" s="17"/>
-      <c r="D54" s="17"/>
-      <c r="E54" s="17"/>
-      <c r="F54" s="17"/>
-      <c r="G54" s="17"/>
-      <c r="H54" s="17"/>
-      <c r="I54" s="17"/>
-      <c r="J54" s="17"/>
-      <c r="K54" s="17"/>
-    </row>
-    <row r="55" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="2">
+    <row r="36" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="2">
         <v>7</v>
       </c>
-      <c r="B55" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C55" s="3">
+      <c r="B36" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C36" s="3">
         <v>1</v>
       </c>
-      <c r="D55" s="4"/>
-      <c r="E55" s="5"/>
-      <c r="F55" s="5"/>
-      <c r="G55" s="7">
-        <f t="shared" ref="G55" si="0">PRODUCT(C55:F55)</f>
+      <c r="D36" s="4"/>
+      <c r="E36" s="5"/>
+      <c r="F36" s="5"/>
+      <c r="G36" s="7">
+        <f t="shared" ref="G36" si="0">PRODUCT(C36:F36)</f>
         <v>1</v>
       </c>
-      <c r="H55" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="I55" s="6">
+      <c r="H36" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="I36" s="6">
         <v>5000</v>
       </c>
-      <c r="J55" s="7">
-        <f>G55*I55</f>
+      <c r="J36" s="7">
+        <f>G36*I36</f>
         <v>5000</v>
       </c>
-      <c r="K55" s="5"/>
-    </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A56" s="2"/>
-      <c r="B56" s="8"/>
-      <c r="C56" s="3"/>
-      <c r="D56" s="4"/>
-      <c r="E56" s="5"/>
-      <c r="F56" s="5"/>
-      <c r="G56" s="6"/>
-      <c r="H56" s="7"/>
-      <c r="I56" s="6"/>
-      <c r="J56" s="18"/>
-      <c r="K56" s="5"/>
-    </row>
-    <row r="57" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="2">
+      <c r="K36" s="5"/>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A37" s="2"/>
+      <c r="B37" s="8"/>
+      <c r="C37" s="3"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="5"/>
+      <c r="F37" s="5"/>
+      <c r="G37" s="6"/>
+      <c r="H37" s="7"/>
+      <c r="I37" s="6"/>
+      <c r="J37" s="18"/>
+      <c r="K37" s="5"/>
+    </row>
+    <row r="38" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="2">
         <v>8</v>
       </c>
-      <c r="B57" s="1" t="s">
+      <c r="B38" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C57" s="3">
+      <c r="C38" s="3">
         <v>1</v>
       </c>
-      <c r="D57" s="4"/>
-      <c r="E57" s="5"/>
-      <c r="F57" s="5"/>
-      <c r="G57" s="7">
-        <f t="shared" ref="G57" si="1">PRODUCT(C57:F57)</f>
+      <c r="D38" s="4"/>
+      <c r="E38" s="5"/>
+      <c r="F38" s="5"/>
+      <c r="G38" s="7">
+        <f t="shared" ref="G38" si="1">PRODUCT(C38:F38)</f>
         <v>1</v>
       </c>
-      <c r="H57" s="7" t="s">
+      <c r="H38" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="I57" s="6">
+      <c r="I38" s="6">
         <v>500</v>
       </c>
-      <c r="J57" s="7">
-        <f>G57*I57</f>
+      <c r="J38" s="7">
+        <f>G38*I38</f>
         <v>500</v>
       </c>
-      <c r="K57" s="5"/>
-    </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A58" s="2"/>
-      <c r="B58" s="8"/>
-      <c r="C58" s="3"/>
-      <c r="D58" s="4"/>
-      <c r="E58" s="5"/>
-      <c r="F58" s="5"/>
-      <c r="G58" s="6"/>
-      <c r="H58" s="7"/>
-      <c r="I58" s="6"/>
-      <c r="J58" s="18"/>
-      <c r="K58" s="5"/>
-    </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A59" s="21"/>
-      <c r="B59" s="22" t="s">
+      <c r="K38" s="5"/>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A39" s="2"/>
+      <c r="B39" s="8"/>
+      <c r="C39" s="3"/>
+      <c r="D39" s="4"/>
+      <c r="E39" s="5"/>
+      <c r="F39" s="5"/>
+      <c r="G39" s="6"/>
+      <c r="H39" s="7"/>
+      <c r="I39" s="6"/>
+      <c r="J39" s="18"/>
+      <c r="K39" s="5"/>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A40" s="21"/>
+      <c r="B40" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="C59" s="23"/>
-      <c r="D59" s="24"/>
-      <c r="E59" s="24"/>
-      <c r="F59" s="24"/>
-      <c r="G59" s="18"/>
-      <c r="H59" s="18"/>
-      <c r="I59" s="18"/>
-      <c r="J59" s="18">
-        <f>SUM(J9:J57)</f>
-        <v>419878.03175496001</v>
-      </c>
-      <c r="K59" s="25"/>
-    </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="M60" s="20"/>
-      <c r="N60" s="20"/>
-      <c r="O60" s="20"/>
-      <c r="P60" s="20"/>
-      <c r="Q60" s="20"/>
-      <c r="R60" s="20"/>
-      <c r="S60" s="20"/>
-    </row>
-    <row r="61" spans="1:19" s="20" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="26"/>
-      <c r="B61" s="27" t="s">
+      <c r="C40" s="23"/>
+      <c r="D40" s="24"/>
+      <c r="E40" s="24"/>
+      <c r="F40" s="24"/>
+      <c r="G40" s="18"/>
+      <c r="H40" s="18"/>
+      <c r="I40" s="18"/>
+      <c r="J40" s="18">
+        <f>SUM(J9:J38)</f>
+        <v>429467.02421124995</v>
+      </c>
+      <c r="K40" s="25"/>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="M41" s="20"/>
+      <c r="N41" s="20"/>
+      <c r="O41" s="20"/>
+      <c r="P41" s="20"/>
+      <c r="Q41" s="20"/>
+      <c r="R41" s="20"/>
+      <c r="S41" s="20"/>
+    </row>
+    <row r="42" spans="1:19" s="20" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="26"/>
+      <c r="B42" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="C61" s="39">
-        <f>J59</f>
-        <v>419878.03175496001</v>
-      </c>
-      <c r="D61" s="40"/>
-      <c r="E61" s="9">
-        <v>100</v>
-      </c>
-      <c r="F61" s="26"/>
-      <c r="G61" s="28"/>
-      <c r="H61" s="26"/>
-      <c r="I61" s="29"/>
-      <c r="J61" s="30"/>
-      <c r="K61" s="31"/>
-      <c r="M61" s="19"/>
-      <c r="N61" s="19"/>
-      <c r="O61" s="19"/>
-      <c r="P61" s="19"/>
-      <c r="Q61" s="19"/>
-      <c r="R61" s="19"/>
-      <c r="S61" s="19"/>
-    </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B62" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="C62" s="43">
-        <v>375000</v>
-      </c>
-      <c r="D62" s="44"/>
-      <c r="E62" s="9"/>
-    </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B63" s="27" t="s">
-        <v>24</v>
-      </c>
-      <c r="C63" s="43">
-        <f>C62-C65-C66</f>
-        <v>356250</v>
-      </c>
-      <c r="D63" s="44"/>
-      <c r="E63" s="9">
-        <f>C63/C61*100</f>
-        <v>84.84606791905388</v>
-      </c>
-    </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B64" s="27" t="s">
-        <v>35</v>
-      </c>
-      <c r="C64" s="45">
-        <f>C61-C63</f>
-        <v>63628.031754960015</v>
-      </c>
-      <c r="D64" s="45"/>
-      <c r="E64" s="9">
-        <f>100-E63</f>
-        <v>15.15393208094612</v>
-      </c>
-    </row>
-    <row r="65" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B65" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="C65" s="39">
-        <f>C62*0.03</f>
-        <v>11250</v>
-      </c>
-      <c r="D65" s="40"/>
-      <c r="E65" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="66" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B66" s="27" t="s">
-        <v>26</v>
-      </c>
-      <c r="C66" s="39">
-        <f>C62*0.02</f>
-        <v>7500</v>
-      </c>
-      <c r="D66" s="40"/>
-      <c r="E66" s="9">
-        <v>2</v>
-      </c>
+      <c r="C42" s="44">
+        <f>J40</f>
+        <v>429467.02421124995</v>
+      </c>
+      <c r="D42" s="45"/>
+      <c r="E42" s="9"/>
+      <c r="F42" s="26"/>
+      <c r="G42" s="28"/>
+      <c r="H42" s="26"/>
+      <c r="I42" s="29"/>
+      <c r="J42" s="30"/>
+      <c r="K42" s="31"/>
+      <c r="M42" s="19"/>
+      <c r="N42" s="19"/>
+      <c r="O42" s="19"/>
+      <c r="P42" s="19"/>
+      <c r="Q42" s="19"/>
+      <c r="R42" s="19"/>
+      <c r="S42" s="19"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="10">
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="H7:K7"/>
+    <mergeCell ref="C42:D42"/>
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="H6:K6"/>
     <mergeCell ref="A1:K1"/>
@@ -2416,14 +1951,6 @@
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A4:K4"/>
     <mergeCell ref="A5:K5"/>
-    <mergeCell ref="C65:D65"/>
-    <mergeCell ref="C66:D66"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="H7:K7"/>
-    <mergeCell ref="C61:D61"/>
-    <mergeCell ref="C62:D62"/>
-    <mergeCell ref="C63:D63"/>
-    <mergeCell ref="C64:D64"/>
   </mergeCells>
   <pageMargins left="0.70866141732283505" right="0.70866141732283505" top="0.74803149606299202" bottom="0.74803149606299202" header="0.31496062992126" footer="0.31496062992126"/>
   <pageSetup paperSize="9" scale="80" orientation="portrait" verticalDpi="1200" r:id="rId1"/>
